--- a/docs/downloads/control_matrix.xlsx
+++ b/docs/downloads/control_matrix.xlsx
@@ -2231,7 +2231,7 @@
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>Product description accurately states that detection is rules-based (no LLM) and how outputs are produced</t>
+          <t>README states intended use, known limitations, that the tool is rules-based with no LLM, and its not-for-production status</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
@@ -2251,7 +2251,7 @@
       </c>
       <c r="G28" s="7" t="inlineStr">
         <is>
-          <t>Not in place. README line 5 positions the tool as a small-scale version of AI-native products and the title says 'Agent', without saying that no model is used.</t>
+          <t>Not in place. The README does not state intended use, limits on real books, false negatives or production status.</t>
         </is>
       </c>
       <c r="H28" s="7" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="K28" s="7" t="inlineStr">
         <is>
-          <t>Not in place (confirmed: README line 5 positions the tool as a small-scale version of AI-native products and the title says 'Agent'; no statement that no model is used)</t>
+          <t>Not in place (confirmed: no such statement in the README)</t>
         </is>
       </c>
     </row>
@@ -3012,7 +3012,7 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>Reviewers over-rely on the tool because of the 'AI-native' label and the 7/7 headline</t>
+          <t>Reviewers over-rely on the tool because of the 7/7 headline</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B30" s="7" t="inlineStr">
         <is>
-          <t>Ambiguous 'AI-native' and 'agent' positioning of a rules-based system: the README never says no model is used</t>
+          <t>Users are not told what the tool cannot detect, its known limits or that it is not for production use</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
